--- a/Samples/8. Optimization/Optimization.xlsx
+++ b/Samples/8. Optimization/Optimization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dimit\Documents\School\Gamedev\GameDevSamples\Samples\8. Optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EA80B6-A156-4B78-812A-AC9AE3E54023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95654B2-6B1B-467A-8D5A-7047A4050E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -412,6 +412,9 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>60</v>
       </c>

--- a/Samples/8. Optimization/Optimization.xlsx
+++ b/Samples/8. Optimization/Optimization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dimit\Documents\School\Gamedev\GameDevSamples\Samples\8. Optimization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\School\GameDev\GameDevSamples\Samples\8. Optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95654B2-6B1B-467A-8D5A-7047A4050E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFFBC3D-EA86-4FD6-A665-13DAB9169DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>#</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>Effects Functionality</t>
+  </si>
+  <si>
+    <t>Tested On</t>
+  </si>
+  <si>
+    <t>Desktop</t>
   </si>
 </sst>
 </file>
@@ -91,7 +97,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -369,20 +375,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -410,8 +417,11 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -420,6 +430,9 @@
       </c>
       <c r="D2">
         <v>60</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
